--- a/data/trans_dic/P21D_2_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,22</t>
+          <t>2,23; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,65</t>
+          <t>2,75; 10,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,53</t>
+          <t>2,97; 7,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,45</t>
+          <t>0,61; 2,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,92</t>
+          <t>1,24; 2,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,27</t>
+          <t>1,05; 2,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,32</t>
+          <t>0,88; 2,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,63</t>
+          <t>1,61; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,6</t>
+          <t>1,39; 2,55</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5007; 16663</t>
+          <t>5140; 17547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8655; 35969</t>
+          <t>9278; 36253</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17027; 48478</t>
+          <t>16862; 44154</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7329; 27361</t>
+          <t>6792; 26427</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11865; 27327</t>
+          <t>11607; 27542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22343; 46657</t>
+          <t>21589; 48305</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>508; 4522</t>
+          <t>512; 4878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>509; 4871</t>
+          <t>505; 4767</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15085; 38432</t>
+          <t>14622; 37830</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25844; 57500</t>
+          <t>25580; 57131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45886; 84447</t>
+          <t>45160; 82590</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_2_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,6</t>
+          <t>2,28; 6,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,73</t>
+          <t>2,23; 5,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,76</t>
+          <t>2,58; 5,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,37</t>
+          <t>1,51; 3,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,94</t>
+          <t>1,86; 3,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,35</t>
+          <t>1,86; 3,31</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,57</t>
+          <t>0,15; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,07; 0,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,28</t>
+          <t>1,53; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,6</t>
+          <t>1,78; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,55</t>
+          <t>1,79; 2,84</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>22765</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5140; 17547</t>
+          <t>5774; 17566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9278; 36253</t>
+          <t>8103; 19731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16862; 44154</t>
+          <t>15959; 32719</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>49675</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6792; 26427</t>
+          <t>14465; 36262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11607; 27542</t>
+          <t>18333; 38060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21589; 48305</t>
+          <t>36117; 64311</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>512; 4878</t>
+          <t>498; 4589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>505; 4767</t>
+          <t>514; 5742</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14622; 37830</t>
+          <t>23859; 47091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25580; 57131</t>
+          <t>30086; 53385</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45160; 82590</t>
+          <t>58182; 92224</t>
         </is>
       </c>
     </row>
